--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="233">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -711,6 +711,9 @@
   <si>
     <t>['33', '88']</t>
   </si>
+  <si>
+    <t>['64']</t>
+  </si>
 </sst>
 </file>
 
@@ -1071,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP109"/>
+  <dimension ref="A1:BP112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1408,7 +1411,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ2">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1820,7 +1823,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2023,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ5">
         <v>1.11</v>
@@ -2641,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ8">
         <v>0.67</v>
@@ -2847,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3465,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ12">
         <v>0.78</v>
@@ -3880,7 +3883,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ14">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4704,7 +4707,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR18">
         <v>1.45</v>
@@ -4907,7 +4910,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ19">
         <v>1.56</v>
@@ -5319,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ21">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR21">
         <v>1.73</v>
@@ -5734,7 +5737,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ23">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR23">
         <v>1.97</v>
@@ -6349,7 +6352,7 @@
         <v>1.5</v>
       </c>
       <c r="AP26">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ26">
         <v>1.56</v>
@@ -6558,7 +6561,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ27">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR27">
         <v>1.37</v>
@@ -7173,7 +7176,7 @@
         <v>2</v>
       </c>
       <c r="AP30">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ30">
         <v>1.56</v>
@@ -7382,7 +7385,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ31">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR31">
         <v>1.23</v>
@@ -7585,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -8206,7 +8209,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ35">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR35">
         <v>1.92</v>
@@ -9439,7 +9442,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ41">
         <v>1.33</v>
@@ -10060,7 +10063,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ44">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR44">
         <v>1.17</v>
@@ -10263,7 +10266,7 @@
         <v>0.33</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -10469,10 +10472,10 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ46">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR46">
         <v>1.42</v>
@@ -11090,7 +11093,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ49">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR49">
         <v>1.86</v>
@@ -11293,7 +11296,7 @@
         <v>0.25</v>
       </c>
       <c r="AP50">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ50">
         <v>0.78</v>
@@ -11708,7 +11711,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ52">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR52">
         <v>1.22</v>
@@ -12735,7 +12738,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ57">
         <v>1.67</v>
@@ -12941,7 +12944,7 @@
         <v>0.75</v>
       </c>
       <c r="AP58">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ58">
         <v>1.11</v>
@@ -13150,7 +13153,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ59">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR59">
         <v>1.76</v>
@@ -13356,7 +13359,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ60">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR60">
         <v>1.68</v>
@@ -13768,7 +13771,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ62">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR62">
         <v>1.82</v>
@@ -14383,10 +14386,10 @@
         <v>0.8</v>
       </c>
       <c r="AP65">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ65">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR65">
         <v>1.56</v>
@@ -15207,7 +15210,7 @@
         <v>2</v>
       </c>
       <c r="AP69">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ69">
         <v>1.56</v>
@@ -15416,7 +15419,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ70">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR70">
         <v>1.6</v>
@@ -15619,7 +15622,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ71">
         <v>1.56</v>
@@ -16031,7 +16034,7 @@
         <v>1.6</v>
       </c>
       <c r="AP73">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ73">
         <v>1.67</v>
@@ -16446,7 +16449,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ75">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR75">
         <v>1.69</v>
@@ -17270,7 +17273,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ79">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR79">
         <v>1.77</v>
@@ -17885,7 +17888,7 @@
         <v>2.17</v>
       </c>
       <c r="AP82">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ82">
         <v>1.56</v>
@@ -18091,7 +18094,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ83">
         <v>1.67</v>
@@ -18300,7 +18303,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ84">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR84">
         <v>1.54</v>
@@ -18503,7 +18506,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ85">
         <v>1.33</v>
@@ -18918,7 +18921,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ87">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR87">
         <v>1.52</v>
@@ -20360,7 +20363,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ94">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR94">
         <v>1.49</v>
@@ -20769,7 +20772,7 @@
         <v>1.29</v>
       </c>
       <c r="AP96">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ96">
         <v>1.33</v>
@@ -20975,10 +20978,10 @@
         <v>1.14</v>
       </c>
       <c r="AP97">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ97">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR97">
         <v>1.72</v>
@@ -21387,7 +21390,7 @@
         <v>0.75</v>
       </c>
       <c r="AP99">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ99">
         <v>0.67</v>
@@ -22005,10 +22008,10 @@
         <v>0.25</v>
       </c>
       <c r="AP102">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ102">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AR102">
         <v>1.93</v>
@@ -22832,7 +22835,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ106">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR106">
         <v>1.73</v>
@@ -23035,7 +23038,7 @@
         <v>1.38</v>
       </c>
       <c r="AP107">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ107">
         <v>1.22</v>
@@ -23450,7 +23453,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ109">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR109">
         <v>1.41</v>
@@ -23526,6 +23529,624 @@
       </c>
       <c r="BP109">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7487137</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45675.58333333334</v>
+      </c>
+      <c r="F110">
+        <v>19</v>
+      </c>
+      <c r="G110" t="s">
+        <v>73</v>
+      </c>
+      <c r="H110" t="s">
+        <v>72</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110" t="s">
+        <v>83</v>
+      </c>
+      <c r="P110" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q110">
+        <v>1.73</v>
+      </c>
+      <c r="R110">
+        <v>2.75</v>
+      </c>
+      <c r="S110">
+        <v>7</v>
+      </c>
+      <c r="T110">
+        <v>1.25</v>
+      </c>
+      <c r="U110">
+        <v>3.75</v>
+      </c>
+      <c r="V110">
+        <v>2.1</v>
+      </c>
+      <c r="W110">
+        <v>1.67</v>
+      </c>
+      <c r="X110">
+        <v>5</v>
+      </c>
+      <c r="Y110">
+        <v>1.17</v>
+      </c>
+      <c r="Z110">
+        <v>1.33</v>
+      </c>
+      <c r="AA110">
+        <v>5.25</v>
+      </c>
+      <c r="AB110">
+        <v>8.75</v>
+      </c>
+      <c r="AC110">
+        <v>1.01</v>
+      </c>
+      <c r="AD110">
+        <v>17</v>
+      </c>
+      <c r="AE110">
+        <v>1.12</v>
+      </c>
+      <c r="AF110">
+        <v>6</v>
+      </c>
+      <c r="AG110">
+        <v>1.42</v>
+      </c>
+      <c r="AH110">
+        <v>2.74</v>
+      </c>
+      <c r="AI110">
+        <v>1.73</v>
+      </c>
+      <c r="AJ110">
+        <v>2</v>
+      </c>
+      <c r="AK110">
+        <v>1.07</v>
+      </c>
+      <c r="AL110">
+        <v>1.14</v>
+      </c>
+      <c r="AM110">
+        <v>3.3</v>
+      </c>
+      <c r="AN110">
+        <v>1.89</v>
+      </c>
+      <c r="AO110">
+        <v>0.33</v>
+      </c>
+      <c r="AP110">
+        <v>1.8</v>
+      </c>
+      <c r="AQ110">
+        <v>0.4</v>
+      </c>
+      <c r="AR110">
+        <v>1.84</v>
+      </c>
+      <c r="AS110">
+        <v>1.16</v>
+      </c>
+      <c r="AT110">
+        <v>3</v>
+      </c>
+      <c r="AU110">
+        <v>9</v>
+      </c>
+      <c r="AV110">
+        <v>3</v>
+      </c>
+      <c r="AW110">
+        <v>17</v>
+      </c>
+      <c r="AX110">
+        <v>6</v>
+      </c>
+      <c r="AY110">
+        <v>30</v>
+      </c>
+      <c r="AZ110">
+        <v>11</v>
+      </c>
+      <c r="BA110">
+        <v>11</v>
+      </c>
+      <c r="BB110">
+        <v>3</v>
+      </c>
+      <c r="BC110">
+        <v>14</v>
+      </c>
+      <c r="BD110">
+        <v>1.24</v>
+      </c>
+      <c r="BE110">
+        <v>8.5</v>
+      </c>
+      <c r="BF110">
+        <v>4.3</v>
+      </c>
+      <c r="BG110">
+        <v>1.12</v>
+      </c>
+      <c r="BH110">
+        <v>4.9</v>
+      </c>
+      <c r="BI110">
+        <v>1.23</v>
+      </c>
+      <c r="BJ110">
+        <v>3.55</v>
+      </c>
+      <c r="BK110">
+        <v>1.4</v>
+      </c>
+      <c r="BL110">
+        <v>2.65</v>
+      </c>
+      <c r="BM110">
+        <v>1.82</v>
+      </c>
+      <c r="BN110">
+        <v>1.98</v>
+      </c>
+      <c r="BO110">
+        <v>1.94</v>
+      </c>
+      <c r="BP110">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7487136</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45675.58333333334</v>
+      </c>
+      <c r="F111">
+        <v>19</v>
+      </c>
+      <c r="G111" t="s">
+        <v>77</v>
+      </c>
+      <c r="H111" t="s">
+        <v>78</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>1</v>
+      </c>
+      <c r="N111">
+        <v>1</v>
+      </c>
+      <c r="O111" t="s">
+        <v>83</v>
+      </c>
+      <c r="P111" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q111">
+        <v>2.63</v>
+      </c>
+      <c r="R111">
+        <v>2.1</v>
+      </c>
+      <c r="S111">
+        <v>4.5</v>
+      </c>
+      <c r="T111">
+        <v>1.44</v>
+      </c>
+      <c r="U111">
+        <v>2.63</v>
+      </c>
+      <c r="V111">
+        <v>3.25</v>
+      </c>
+      <c r="W111">
+        <v>1.33</v>
+      </c>
+      <c r="X111">
+        <v>9</v>
+      </c>
+      <c r="Y111">
+        <v>1.07</v>
+      </c>
+      <c r="Z111">
+        <v>2</v>
+      </c>
+      <c r="AA111">
+        <v>3.4</v>
+      </c>
+      <c r="AB111">
+        <v>3.75</v>
+      </c>
+      <c r="AC111">
+        <v>1.06</v>
+      </c>
+      <c r="AD111">
+        <v>8.5</v>
+      </c>
+      <c r="AE111">
+        <v>1.36</v>
+      </c>
+      <c r="AF111">
+        <v>3</v>
+      </c>
+      <c r="AG111">
+        <v>2.07</v>
+      </c>
+      <c r="AH111">
+        <v>1.71</v>
+      </c>
+      <c r="AI111">
+        <v>1.91</v>
+      </c>
+      <c r="AJ111">
+        <v>1.8</v>
+      </c>
+      <c r="AK111">
+        <v>1.26</v>
+      </c>
+      <c r="AL111">
+        <v>1.31</v>
+      </c>
+      <c r="AM111">
+        <v>1.77</v>
+      </c>
+      <c r="AN111">
+        <v>1.78</v>
+      </c>
+      <c r="AO111">
+        <v>0.78</v>
+      </c>
+      <c r="AP111">
+        <v>1.6</v>
+      </c>
+      <c r="AQ111">
+        <v>1</v>
+      </c>
+      <c r="AR111">
+        <v>1.55</v>
+      </c>
+      <c r="AS111">
+        <v>1.38</v>
+      </c>
+      <c r="AT111">
+        <v>2.93</v>
+      </c>
+      <c r="AU111">
+        <v>7</v>
+      </c>
+      <c r="AV111">
+        <v>4</v>
+      </c>
+      <c r="AW111">
+        <v>19</v>
+      </c>
+      <c r="AX111">
+        <v>1</v>
+      </c>
+      <c r="AY111">
+        <v>27</v>
+      </c>
+      <c r="AZ111">
+        <v>5</v>
+      </c>
+      <c r="BA111">
+        <v>9</v>
+      </c>
+      <c r="BB111">
+        <v>2</v>
+      </c>
+      <c r="BC111">
+        <v>11</v>
+      </c>
+      <c r="BD111">
+        <v>1.64</v>
+      </c>
+      <c r="BE111">
+        <v>6.4</v>
+      </c>
+      <c r="BF111">
+        <v>2.55</v>
+      </c>
+      <c r="BG111">
+        <v>1.36</v>
+      </c>
+      <c r="BH111">
+        <v>2.8</v>
+      </c>
+      <c r="BI111">
+        <v>1.6</v>
+      </c>
+      <c r="BJ111">
+        <v>2.14</v>
+      </c>
+      <c r="BK111">
+        <v>1.98</v>
+      </c>
+      <c r="BL111">
+        <v>1.71</v>
+      </c>
+      <c r="BM111">
+        <v>2.5</v>
+      </c>
+      <c r="BN111">
+        <v>1.44</v>
+      </c>
+      <c r="BO111">
+        <v>3.3</v>
+      </c>
+      <c r="BP111">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7487135</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45675.6875</v>
+      </c>
+      <c r="F112">
+        <v>19</v>
+      </c>
+      <c r="G112" t="s">
+        <v>76</v>
+      </c>
+      <c r="H112" t="s">
+        <v>80</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>1</v>
+      </c>
+      <c r="M112">
+        <v>1</v>
+      </c>
+      <c r="N112">
+        <v>2</v>
+      </c>
+      <c r="O112" t="s">
+        <v>84</v>
+      </c>
+      <c r="P112" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q112">
+        <v>2.3</v>
+      </c>
+      <c r="R112">
+        <v>2.4</v>
+      </c>
+      <c r="S112">
+        <v>4.5</v>
+      </c>
+      <c r="T112">
+        <v>1.29</v>
+      </c>
+      <c r="U112">
+        <v>3.5</v>
+      </c>
+      <c r="V112">
+        <v>2.38</v>
+      </c>
+      <c r="W112">
+        <v>1.53</v>
+      </c>
+      <c r="X112">
+        <v>5.5</v>
+      </c>
+      <c r="Y112">
+        <v>1.14</v>
+      </c>
+      <c r="Z112">
+        <v>1.9</v>
+      </c>
+      <c r="AA112">
+        <v>3.55</v>
+      </c>
+      <c r="AB112">
+        <v>3.95</v>
+      </c>
+      <c r="AC112">
+        <v>1.04</v>
+      </c>
+      <c r="AD112">
+        <v>10</v>
+      </c>
+      <c r="AE112">
+        <v>1.18</v>
+      </c>
+      <c r="AF112">
+        <v>4.75</v>
+      </c>
+      <c r="AG112">
+        <v>1.58</v>
+      </c>
+      <c r="AH112">
+        <v>2.28</v>
+      </c>
+      <c r="AI112">
+        <v>1.57</v>
+      </c>
+      <c r="AJ112">
+        <v>2.25</v>
+      </c>
+      <c r="AK112">
+        <v>1.18</v>
+      </c>
+      <c r="AL112">
+        <v>1.18</v>
+      </c>
+      <c r="AM112">
+        <v>2.05</v>
+      </c>
+      <c r="AN112">
+        <v>2</v>
+      </c>
+      <c r="AO112">
+        <v>1.22</v>
+      </c>
+      <c r="AP112">
+        <v>1.9</v>
+      </c>
+      <c r="AQ112">
+        <v>1.2</v>
+      </c>
+      <c r="AR112">
+        <v>1.84</v>
+      </c>
+      <c r="AS112">
+        <v>1.39</v>
+      </c>
+      <c r="AT112">
+        <v>3.23</v>
+      </c>
+      <c r="AU112">
+        <v>5</v>
+      </c>
+      <c r="AV112">
+        <v>5</v>
+      </c>
+      <c r="AW112">
+        <v>20</v>
+      </c>
+      <c r="AX112">
+        <v>6</v>
+      </c>
+      <c r="AY112">
+        <v>35</v>
+      </c>
+      <c r="AZ112">
+        <v>11</v>
+      </c>
+      <c r="BA112">
+        <v>11</v>
+      </c>
+      <c r="BB112">
+        <v>3</v>
+      </c>
+      <c r="BC112">
+        <v>14</v>
+      </c>
+      <c r="BD112">
+        <v>1.54</v>
+      </c>
+      <c r="BE112">
+        <v>7</v>
+      </c>
+      <c r="BF112">
+        <v>2.65</v>
+      </c>
+      <c r="BG112">
+        <v>1.14</v>
+      </c>
+      <c r="BH112">
+        <v>4.6</v>
+      </c>
+      <c r="BI112">
+        <v>1.26</v>
+      </c>
+      <c r="BJ112">
+        <v>3.3</v>
+      </c>
+      <c r="BK112">
+        <v>1.46</v>
+      </c>
+      <c r="BL112">
+        <v>2.45</v>
+      </c>
+      <c r="BM112">
+        <v>1.82</v>
+      </c>
+      <c r="BN112">
+        <v>1.98</v>
+      </c>
+      <c r="BO112">
+        <v>2.12</v>
+      </c>
+      <c r="BP112">
+        <v>1.62</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Switzerland Super League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Switzerland Super League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="235">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -520,6 +520,9 @@
     <t>['68']</t>
   </si>
   <si>
+    <t>['45+2', '53']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
@@ -713,6 +716,9 @@
   </si>
   <si>
     <t>['64']</t>
+  </si>
+  <si>
+    <t>['24', '87']</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP112"/>
+  <dimension ref="A1:BP115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1330,7 +1336,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1408,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -1536,7 +1542,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1948,7 +1954,7 @@
         <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q5">
         <v>1.91</v>
@@ -2154,7 +2160,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2232,10 +2238,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ6">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2360,7 +2366,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2566,7 +2572,7 @@
         <v>88</v>
       </c>
       <c r="P8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q8">
         <v>2.45</v>
@@ -2978,7 +2984,7 @@
         <v>90</v>
       </c>
       <c r="P10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q10">
         <v>2.85</v>
@@ -3059,7 +3065,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ10">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3184,7 +3190,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q11">
         <v>2.9</v>
@@ -3390,7 +3396,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -3471,7 +3477,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ12">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR12">
         <v>2.07</v>
@@ -3802,7 +3808,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q14">
         <v>2.1</v>
@@ -3880,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ14">
         <v>0.4</v>
@@ -4008,7 +4014,7 @@
         <v>83</v>
       </c>
       <c r="P15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q15">
         <v>3.05</v>
@@ -4089,7 +4095,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ15">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR15">
         <v>1.44</v>
@@ -4292,7 +4298,7 @@
         <v>3</v>
       </c>
       <c r="AP16">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>1.22</v>
@@ -4626,7 +4632,7 @@
         <v>97</v>
       </c>
       <c r="P18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4704,7 +4710,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ18">
         <v>1.2</v>
@@ -4832,7 +4838,7 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q19">
         <v>2.6</v>
@@ -5119,7 +5125,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ20">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR20">
         <v>1.02</v>
@@ -5450,7 +5456,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q22">
         <v>4.33</v>
@@ -5862,7 +5868,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -5940,10 +5946,10 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ24">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR24">
         <v>1.94</v>
@@ -6146,7 +6152,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ25">
         <v>1</v>
@@ -6274,7 +6280,7 @@
         <v>83</v>
       </c>
       <c r="P26" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -6355,7 +6361,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ26">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR26">
         <v>1.85</v>
@@ -6686,7 +6692,7 @@
         <v>105</v>
       </c>
       <c r="P28" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q28">
         <v>3.4</v>
@@ -6973,7 +6979,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ29">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR29">
         <v>2.04</v>
@@ -7098,7 +7104,7 @@
         <v>107</v>
       </c>
       <c r="P30" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -7179,7 +7185,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ30">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR30">
         <v>1.76</v>
@@ -7304,7 +7310,7 @@
         <v>108</v>
       </c>
       <c r="P31" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -8000,10 +8006,10 @@
         <v>2</v>
       </c>
       <c r="AP34">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ34">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR34">
         <v>2.41</v>
@@ -8128,7 +8134,7 @@
         <v>111</v>
       </c>
       <c r="P35" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q35">
         <v>2.7</v>
@@ -8206,7 +8212,7 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ35">
         <v>1.2</v>
@@ -8334,7 +8340,7 @@
         <v>87</v>
       </c>
       <c r="P36" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -8412,7 +8418,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ36">
         <v>1.33</v>
@@ -8540,7 +8546,7 @@
         <v>112</v>
       </c>
       <c r="P37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q37">
         <v>2.4</v>
@@ -8621,7 +8627,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ37">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR37">
         <v>1.76</v>
@@ -8746,7 +8752,7 @@
         <v>113</v>
       </c>
       <c r="P38" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q38">
         <v>4</v>
@@ -8952,7 +8958,7 @@
         <v>83</v>
       </c>
       <c r="P39" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -9158,7 +9164,7 @@
         <v>114</v>
       </c>
       <c r="P40" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q40">
         <v>2.2</v>
@@ -9236,10 +9242,10 @@
         <v>0.33</v>
       </c>
       <c r="AP40">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ40">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR40">
         <v>1.54</v>
@@ -9570,7 +9576,7 @@
         <v>115</v>
       </c>
       <c r="P42" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q42">
         <v>4.33</v>
@@ -9776,7 +9782,7 @@
         <v>116</v>
       </c>
       <c r="P43" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -10394,7 +10400,7 @@
         <v>83</v>
       </c>
       <c r="P46" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -10678,7 +10684,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ47">
         <v>1.11</v>
@@ -10887,7 +10893,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ48">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR48">
         <v>1.38</v>
@@ -11012,7 +11018,7 @@
         <v>121</v>
       </c>
       <c r="P49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q49">
         <v>2.05</v>
@@ -11090,7 +11096,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ49">
         <v>0.4</v>
@@ -11218,7 +11224,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q50">
         <v>2.09</v>
@@ -11299,7 +11305,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ50">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR50">
         <v>1.38</v>
@@ -11424,7 +11430,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q51">
         <v>2.64</v>
@@ -11914,7 +11920,7 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ53">
         <v>1.33</v>
@@ -12248,7 +12254,7 @@
         <v>127</v>
       </c>
       <c r="P55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q55">
         <v>2.65</v>
@@ -12454,7 +12460,7 @@
         <v>128</v>
       </c>
       <c r="P56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q56">
         <v>3.5</v>
@@ -12741,7 +12747,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ57">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR57">
         <v>1.51</v>
@@ -13072,7 +13078,7 @@
         <v>131</v>
       </c>
       <c r="P59" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13356,7 +13362,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ60">
         <v>0.4</v>
@@ -13768,7 +13774,7 @@
         <v>0.6</v>
       </c>
       <c r="AP62">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ62">
         <v>1</v>
@@ -13896,7 +13902,7 @@
         <v>135</v>
       </c>
       <c r="P63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
@@ -13977,7 +13983,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ63">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR63">
         <v>1.26</v>
@@ -14102,7 +14108,7 @@
         <v>136</v>
       </c>
       <c r="P64" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q64">
         <v>1.85</v>
@@ -14183,7 +14189,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ64">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR64">
         <v>1.57</v>
@@ -14308,7 +14314,7 @@
         <v>137</v>
       </c>
       <c r="P65" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q65">
         <v>2.88</v>
@@ -14592,7 +14598,7 @@
         <v>0.8</v>
       </c>
       <c r="AP66">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ66">
         <v>0.67</v>
@@ -14720,7 +14726,7 @@
         <v>135</v>
       </c>
       <c r="P67" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q67">
         <v>3.1</v>
@@ -14798,7 +14804,7 @@
         <v>1.6</v>
       </c>
       <c r="AP67">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ67">
         <v>1.22</v>
@@ -14926,7 +14932,7 @@
         <v>83</v>
       </c>
       <c r="P68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15132,7 +15138,7 @@
         <v>83</v>
       </c>
       <c r="P69" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q69">
         <v>2.95</v>
@@ -15338,7 +15344,7 @@
         <v>139</v>
       </c>
       <c r="P70" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q70">
         <v>1.85</v>
@@ -15544,7 +15550,7 @@
         <v>140</v>
       </c>
       <c r="P71" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q71">
         <v>2.5</v>
@@ -15625,7 +15631,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ71">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR71">
         <v>1.55</v>
@@ -15956,7 +15962,7 @@
         <v>142</v>
       </c>
       <c r="P73" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q73">
         <v>2.35</v>
@@ -16037,7 +16043,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ73">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR73">
         <v>1.87</v>
@@ -16240,7 +16246,7 @@
         <v>0.67</v>
       </c>
       <c r="AP74">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ74">
         <v>0.67</v>
@@ -16574,7 +16580,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16858,7 +16864,7 @@
         <v>1.83</v>
       </c>
       <c r="AP77">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ77">
         <v>1.22</v>
@@ -17064,10 +17070,10 @@
         <v>0.83</v>
       </c>
       <c r="AP78">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ78">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR78">
         <v>1.74</v>
@@ -17604,7 +17610,7 @@
         <v>148</v>
       </c>
       <c r="P81" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q81">
         <v>4.5</v>
@@ -17685,7 +17691,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ81">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR81">
         <v>0.99</v>
@@ -17810,7 +17816,7 @@
         <v>109</v>
       </c>
       <c r="P82" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q82">
         <v>2.5</v>
@@ -18016,7 +18022,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
@@ -18097,7 +18103,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ83">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR83">
         <v>1.44</v>
@@ -18222,7 +18228,7 @@
         <v>150</v>
       </c>
       <c r="P84" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q84">
         <v>3.1</v>
@@ -18428,7 +18434,7 @@
         <v>151</v>
       </c>
       <c r="P85" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q85">
         <v>2.7</v>
@@ -18634,7 +18640,7 @@
         <v>152</v>
       </c>
       <c r="P86" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -18840,7 +18846,7 @@
         <v>120</v>
       </c>
       <c r="P87" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -19124,7 +19130,7 @@
         <v>0.67</v>
       </c>
       <c r="AP88">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ88">
         <v>1.11</v>
@@ -19330,7 +19336,7 @@
         <v>2</v>
       </c>
       <c r="AP89">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ89">
         <v>1.56</v>
@@ -19539,7 +19545,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ90">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR90">
         <v>1.67</v>
@@ -19664,7 +19670,7 @@
         <v>155</v>
       </c>
       <c r="P91" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q91">
         <v>2.75</v>
@@ -19870,7 +19876,7 @@
         <v>156</v>
       </c>
       <c r="P92" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q92">
         <v>2.45</v>
@@ -20076,7 +20082,7 @@
         <v>83</v>
       </c>
       <c r="P93" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q93">
         <v>4.2</v>
@@ -20157,7 +20163,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ93">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR93">
         <v>0.95</v>
@@ -20282,7 +20288,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q94">
         <v>2.38</v>
@@ -20360,7 +20366,7 @@
         <v>0.43</v>
       </c>
       <c r="AP94">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20488,7 +20494,7 @@
         <v>144</v>
       </c>
       <c r="P95" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q95">
         <v>4.33</v>
@@ -20900,7 +20906,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q97">
         <v>2.38</v>
@@ -21106,7 +21112,7 @@
         <v>156</v>
       </c>
       <c r="P98" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q98">
         <v>2.1</v>
@@ -21187,7 +21193,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ98">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR98">
         <v>1.52</v>
@@ -21312,7 +21318,7 @@
         <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -21518,7 +21524,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q100">
         <v>3.1</v>
@@ -21802,7 +21808,7 @@
         <v>1.75</v>
       </c>
       <c r="AP101">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ101">
         <v>1.56</v>
@@ -21930,7 +21936,7 @@
         <v>163</v>
       </c>
       <c r="P102" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22136,7 +22142,7 @@
         <v>164</v>
       </c>
       <c r="P103" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -22217,7 +22223,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ103">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR103">
         <v>1.81</v>
@@ -22342,7 +22348,7 @@
         <v>165</v>
       </c>
       <c r="P104" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q104">
         <v>3.7</v>
@@ -22423,7 +22429,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ104">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR104">
         <v>1.23</v>
@@ -22548,7 +22554,7 @@
         <v>83</v>
       </c>
       <c r="P105" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q105">
         <v>4.2</v>
@@ -22960,7 +22966,7 @@
         <v>166</v>
       </c>
       <c r="P107" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q107">
         <v>2.7</v>
@@ -23166,7 +23172,7 @@
         <v>167</v>
       </c>
       <c r="P108" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q108">
         <v>2.5</v>
@@ -23244,7 +23250,7 @@
         <v>0.75</v>
       </c>
       <c r="AP108">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -23372,7 +23378,7 @@
         <v>83</v>
       </c>
       <c r="P109" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23450,7 +23456,7 @@
         <v>1</v>
       </c>
       <c r="AP109">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ109">
         <v>1.2</v>
@@ -23784,7 +23790,7 @@
         <v>83</v>
       </c>
       <c r="P111" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q111">
         <v>2.63</v>
@@ -24147,6 +24153,624 @@
       </c>
       <c r="BP112">
         <v>1.62</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7487138</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45676.42708333334</v>
+      </c>
+      <c r="F113">
+        <v>19</v>
+      </c>
+      <c r="G113" t="s">
+        <v>81</v>
+      </c>
+      <c r="H113" t="s">
+        <v>71</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>1</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>1</v>
+      </c>
+      <c r="O113" t="s">
+        <v>124</v>
+      </c>
+      <c r="P113" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q113">
+        <v>2</v>
+      </c>
+      <c r="R113">
+        <v>2.3</v>
+      </c>
+      <c r="S113">
+        <v>6.5</v>
+      </c>
+      <c r="T113">
+        <v>1.36</v>
+      </c>
+      <c r="U113">
+        <v>3</v>
+      </c>
+      <c r="V113">
+        <v>2.75</v>
+      </c>
+      <c r="W113">
+        <v>1.4</v>
+      </c>
+      <c r="X113">
+        <v>7</v>
+      </c>
+      <c r="Y113">
+        <v>1.1</v>
+      </c>
+      <c r="Z113">
+        <v>1.46</v>
+      </c>
+      <c r="AA113">
+        <v>4.4</v>
+      </c>
+      <c r="AB113">
+        <v>6.54</v>
+      </c>
+      <c r="AC113">
+        <v>1.05</v>
+      </c>
+      <c r="AD113">
+        <v>9.5</v>
+      </c>
+      <c r="AE113">
+        <v>1.25</v>
+      </c>
+      <c r="AF113">
+        <v>3.75</v>
+      </c>
+      <c r="AG113">
+        <v>1.81</v>
+      </c>
+      <c r="AH113">
+        <v>1.93</v>
+      </c>
+      <c r="AI113">
+        <v>2</v>
+      </c>
+      <c r="AJ113">
+        <v>1.73</v>
+      </c>
+      <c r="AK113">
+        <v>1.06</v>
+      </c>
+      <c r="AL113">
+        <v>1.16</v>
+      </c>
+      <c r="AM113">
+        <v>2.65</v>
+      </c>
+      <c r="AN113">
+        <v>1.44</v>
+      </c>
+      <c r="AO113">
+        <v>0.78</v>
+      </c>
+      <c r="AP113">
+        <v>1.6</v>
+      </c>
+      <c r="AQ113">
+        <v>0.7</v>
+      </c>
+      <c r="AR113">
+        <v>1.39</v>
+      </c>
+      <c r="AS113">
+        <v>1.21</v>
+      </c>
+      <c r="AT113">
+        <v>2.6</v>
+      </c>
+      <c r="AU113">
+        <v>4</v>
+      </c>
+      <c r="AV113">
+        <v>6</v>
+      </c>
+      <c r="AW113">
+        <v>12</v>
+      </c>
+      <c r="AX113">
+        <v>3</v>
+      </c>
+      <c r="AY113">
+        <v>20</v>
+      </c>
+      <c r="AZ113">
+        <v>9</v>
+      </c>
+      <c r="BA113">
+        <v>7</v>
+      </c>
+      <c r="BB113">
+        <v>4</v>
+      </c>
+      <c r="BC113">
+        <v>11</v>
+      </c>
+      <c r="BD113">
+        <v>1.35</v>
+      </c>
+      <c r="BE113">
+        <v>7.5</v>
+      </c>
+      <c r="BF113">
+        <v>3.45</v>
+      </c>
+      <c r="BG113">
+        <v>1.23</v>
+      </c>
+      <c r="BH113">
+        <v>3.55</v>
+      </c>
+      <c r="BI113">
+        <v>1.41</v>
+      </c>
+      <c r="BJ113">
+        <v>2.63</v>
+      </c>
+      <c r="BK113">
+        <v>1.66</v>
+      </c>
+      <c r="BL113">
+        <v>2.04</v>
+      </c>
+      <c r="BM113">
+        <v>2.04</v>
+      </c>
+      <c r="BN113">
+        <v>1.66</v>
+      </c>
+      <c r="BO113">
+        <v>2.55</v>
+      </c>
+      <c r="BP113">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7487134</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45676.52083333334</v>
+      </c>
+      <c r="F114">
+        <v>19</v>
+      </c>
+      <c r="G114" t="s">
+        <v>70</v>
+      </c>
+      <c r="H114" t="s">
+        <v>79</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114">
+        <v>1</v>
+      </c>
+      <c r="K114">
+        <v>2</v>
+      </c>
+      <c r="L114">
+        <v>2</v>
+      </c>
+      <c r="M114">
+        <v>2</v>
+      </c>
+      <c r="N114">
+        <v>4</v>
+      </c>
+      <c r="O114" t="s">
+        <v>168</v>
+      </c>
+      <c r="P114" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q114">
+        <v>2.88</v>
+      </c>
+      <c r="R114">
+        <v>2.3</v>
+      </c>
+      <c r="S114">
+        <v>3.25</v>
+      </c>
+      <c r="T114">
+        <v>1.33</v>
+      </c>
+      <c r="U114">
+        <v>3.25</v>
+      </c>
+      <c r="V114">
+        <v>2.5</v>
+      </c>
+      <c r="W114">
+        <v>1.5</v>
+      </c>
+      <c r="X114">
+        <v>6</v>
+      </c>
+      <c r="Y114">
+        <v>1.13</v>
+      </c>
+      <c r="Z114">
+        <v>2.3</v>
+      </c>
+      <c r="AA114">
+        <v>3.5</v>
+      </c>
+      <c r="AB114">
+        <v>2.75</v>
+      </c>
+      <c r="AC114">
+        <v>1.04</v>
+      </c>
+      <c r="AD114">
+        <v>10</v>
+      </c>
+      <c r="AE114">
+        <v>1.2</v>
+      </c>
+      <c r="AF114">
+        <v>4.33</v>
+      </c>
+      <c r="AG114">
+        <v>1.57</v>
+      </c>
+      <c r="AH114">
+        <v>2.15</v>
+      </c>
+      <c r="AI114">
+        <v>1.53</v>
+      </c>
+      <c r="AJ114">
+        <v>2.38</v>
+      </c>
+      <c r="AK114">
+        <v>1.45</v>
+      </c>
+      <c r="AL114">
+        <v>1.22</v>
+      </c>
+      <c r="AM114">
+        <v>1.57</v>
+      </c>
+      <c r="AN114">
+        <v>2.11</v>
+      </c>
+      <c r="AO114">
+        <v>1.56</v>
+      </c>
+      <c r="AP114">
+        <v>2</v>
+      </c>
+      <c r="AQ114">
+        <v>1.5</v>
+      </c>
+      <c r="AR114">
+        <v>1.86</v>
+      </c>
+      <c r="AS114">
+        <v>1.76</v>
+      </c>
+      <c r="AT114">
+        <v>3.62</v>
+      </c>
+      <c r="AU114">
+        <v>6</v>
+      </c>
+      <c r="AV114">
+        <v>6</v>
+      </c>
+      <c r="AW114">
+        <v>14</v>
+      </c>
+      <c r="AX114">
+        <v>16</v>
+      </c>
+      <c r="AY114">
+        <v>25</v>
+      </c>
+      <c r="AZ114">
+        <v>26</v>
+      </c>
+      <c r="BA114">
+        <v>6</v>
+      </c>
+      <c r="BB114">
+        <v>6</v>
+      </c>
+      <c r="BC114">
+        <v>12</v>
+      </c>
+      <c r="BD114">
+        <v>1.93</v>
+      </c>
+      <c r="BE114">
+        <v>6.4</v>
+      </c>
+      <c r="BF114">
+        <v>2.07</v>
+      </c>
+      <c r="BG114">
+        <v>1.33</v>
+      </c>
+      <c r="BH114">
+        <v>2.95</v>
+      </c>
+      <c r="BI114">
+        <v>1.54</v>
+      </c>
+      <c r="BJ114">
+        <v>2.25</v>
+      </c>
+      <c r="BK114">
+        <v>1.85</v>
+      </c>
+      <c r="BL114">
+        <v>1.95</v>
+      </c>
+      <c r="BM114">
+        <v>2.4</v>
+      </c>
+      <c r="BN114">
+        <v>1.48</v>
+      </c>
+      <c r="BO114">
+        <v>3.15</v>
+      </c>
+      <c r="BP114">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7487133</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45676.52083333334</v>
+      </c>
+      <c r="F115">
+        <v>19</v>
+      </c>
+      <c r="G115" t="s">
+        <v>74</v>
+      </c>
+      <c r="H115" t="s">
+        <v>75</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115" t="s">
+        <v>83</v>
+      </c>
+      <c r="P115" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q115">
+        <v>2.5</v>
+      </c>
+      <c r="R115">
+        <v>2.38</v>
+      </c>
+      <c r="S115">
+        <v>3.75</v>
+      </c>
+      <c r="T115">
+        <v>1.3</v>
+      </c>
+      <c r="U115">
+        <v>3.4</v>
+      </c>
+      <c r="V115">
+        <v>2.38</v>
+      </c>
+      <c r="W115">
+        <v>1.53</v>
+      </c>
+      <c r="X115">
+        <v>6</v>
+      </c>
+      <c r="Y115">
+        <v>1.13</v>
+      </c>
+      <c r="Z115">
+        <v>1.95</v>
+      </c>
+      <c r="AA115">
+        <v>3.6</v>
+      </c>
+      <c r="AB115">
+        <v>3.4</v>
+      </c>
+      <c r="AC115">
+        <v>1.04</v>
+      </c>
+      <c r="AD115">
+        <v>10</v>
+      </c>
+      <c r="AE115">
+        <v>1.18</v>
+      </c>
+      <c r="AF115">
+        <v>4.5</v>
+      </c>
+      <c r="AG115">
+        <v>1.55</v>
+      </c>
+      <c r="AH115">
+        <v>2.2</v>
+      </c>
+      <c r="AI115">
+        <v>1.53</v>
+      </c>
+      <c r="AJ115">
+        <v>2.38</v>
+      </c>
+      <c r="AK115">
+        <v>1.22</v>
+      </c>
+      <c r="AL115">
+        <v>1.2</v>
+      </c>
+      <c r="AM115">
+        <v>1.85</v>
+      </c>
+      <c r="AN115">
+        <v>2.33</v>
+      </c>
+      <c r="AO115">
+        <v>1.67</v>
+      </c>
+      <c r="AP115">
+        <v>2.2</v>
+      </c>
+      <c r="AQ115">
+        <v>1.6</v>
+      </c>
+      <c r="AR115">
+        <v>1.76</v>
+      </c>
+      <c r="AS115">
+        <v>1.68</v>
+      </c>
+      <c r="AT115">
+        <v>3.44</v>
+      </c>
+      <c r="AU115">
+        <v>4</v>
+      </c>
+      <c r="AV115">
+        <v>3</v>
+      </c>
+      <c r="AW115">
+        <v>13</v>
+      </c>
+      <c r="AX115">
+        <v>6</v>
+      </c>
+      <c r="AY115">
+        <v>21</v>
+      </c>
+      <c r="AZ115">
+        <v>11</v>
+      </c>
+      <c r="BA115">
+        <v>7</v>
+      </c>
+      <c r="BB115">
+        <v>5</v>
+      </c>
+      <c r="BC115">
+        <v>12</v>
+      </c>
+      <c r="BD115">
+        <v>1.67</v>
+      </c>
+      <c r="BE115">
+        <v>6.75</v>
+      </c>
+      <c r="BF115">
+        <v>2.43</v>
+      </c>
+      <c r="BG115">
+        <v>1.21</v>
+      </c>
+      <c r="BH115">
+        <v>3.8</v>
+      </c>
+      <c r="BI115">
+        <v>1.36</v>
+      </c>
+      <c r="BJ115">
+        <v>2.8</v>
+      </c>
+      <c r="BK115">
+        <v>1.6</v>
+      </c>
+      <c r="BL115">
+        <v>2.14</v>
+      </c>
+      <c r="BM115">
+        <v>1.93</v>
+      </c>
+      <c r="BN115">
+        <v>1.74</v>
+      </c>
+      <c r="BO115">
+        <v>2.43</v>
+      </c>
+      <c r="BP115">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>
